--- a/data/trans_bre/IP1016-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1016-Estudios-trans_bre.xlsx
@@ -719,7 +719,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 0,0</t>
+          <t>-0,53; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
